--- a/eksperimen/eks3_cekout_prob1/perbandingan_split_70vs80.xlsx
+++ b/eksperimen/eks3_cekout_prob1/perbandingan_split_70vs80.xlsx
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7366</v>
+        <v>0.7232</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.5638</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6757</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6289</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="8">
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7321</v>
+        <v>0.7232</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.5714</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.6486</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.6076</v>
       </c>
     </row>
   </sheetData>
@@ -872,16 +872,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7517</v>
+        <v>0.745</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5818</v>
+        <v>0.5714</v>
       </c>
       <c r="F7" t="n">
         <v>0.6957</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6337</v>
+        <v>0.6274999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -926,16 +926,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7651</v>
+        <v>0.7383</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5965</v>
+        <v>0.5593</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7391</v>
+        <v>0.7174</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6602</v>
+        <v>0.6286</v>
       </c>
     </row>
   </sheetData>
@@ -1139,16 +1139,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7366</v>
+        <v>0.7232</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.5638</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6757</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6289</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="8">
@@ -1193,16 +1193,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7321</v>
+        <v>0.7232</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.5714</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.6486</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.6076</v>
       </c>
     </row>
     <row r="10">
@@ -1355,16 +1355,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.7517</v>
+        <v>0.745</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5818</v>
+        <v>0.5714</v>
       </c>
       <c r="F15" t="n">
         <v>0.6957</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6337</v>
+        <v>0.6274999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1409,16 +1409,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.7651</v>
+        <v>0.7383</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5965</v>
+        <v>0.5593</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7391</v>
+        <v>0.7174</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6602</v>
+        <v>0.6286</v>
       </c>
     </row>
   </sheetData>
